--- a/app_kit/tests/TESTS_ROOT/xlsx_for_testing/TaxonProfiles/invalid_content_type/Taxon profiles.xlsx
+++ b/app_kit/tests/TESTS_ROOT/xlsx_for_testing/TaxonProfiles/invalid_content_type/Taxon profiles.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="6">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7" uniqueCount="7">
   <si>
     <t xml:space="preserve">Scientific Names</t>
   </si>
@@ -29,6 +29,9 @@
   </si>
   <si>
     <t xml:space="preserve">Morphotype (optional)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Object class (optional)</t>
   </si>
   <si>
     <t xml:space="preserve">short_profile</t>
@@ -243,37 +246,37 @@
         <a:srgbClr val="000000"/>
       </a:dk1>
       <a:lt1>
-        <a:srgbClr val="ffffff"/>
+        <a:srgbClr val="FFFFFF"/>
       </a:lt1>
       <a:dk2>
         <a:srgbClr val="000000"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="ffffff"/>
+        <a:srgbClr val="FFFFFF"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="18a303"/>
+        <a:srgbClr val="18A303"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="0369a3"/>
+        <a:srgbClr val="0369A3"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="a33e03"/>
+        <a:srgbClr val="A33E03"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="8e03a3"/>
+        <a:srgbClr val="8E03A3"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="c99c00"/>
+        <a:srgbClr val="C99C00"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="c9211e"/>
+        <a:srgbClr val="C9211E"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="0000ee"/>
+        <a:srgbClr val="0000EE"/>
       </a:hlink>
       <a:folHlink>
-        <a:srgbClr val="551a8b"/>
+        <a:srgbClr val="551A8B"/>
       </a:folHlink>
     </a:clrScheme>
     <a:fontScheme name="Office">
@@ -346,12 +349,12 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:AKA4"/>
+  <dimension ref="A1:AKB4"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="33.94"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="2" style="1" width="38.39"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="4" style="1" width="47.98"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="4" style="1" width="47.98"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -365,10 +368,12 @@
       <c r="D1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="E1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="F1" s="4"/>
+      <c r="F1" s="3" t="s">
+        <v>4</v>
+      </c>
       <c r="G1" s="4"/>
       <c r="H1" s="4"/>
       <c r="I1" s="4"/>
@@ -1326,14 +1331,15 @@
       <c r="AJY1" s="4"/>
       <c r="AJZ1" s="4"/>
       <c r="AKA1" s="4"/>
+      <c r="AKB1" s="4"/>
     </row>
     <row r="2" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="2"/>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
       <c r="D2" s="2"/>
-      <c r="E2" s="3"/>
-      <c r="F2" s="4"/>
+      <c r="E2" s="2"/>
+      <c r="F2" s="3"/>
       <c r="G2" s="4"/>
       <c r="H2" s="4"/>
       <c r="I2" s="4"/>
@@ -2291,14 +2297,15 @@
       <c r="AJY2" s="4"/>
       <c r="AJZ2" s="4"/>
       <c r="AKA2" s="4"/>
+      <c r="AKB2" s="4"/>
     </row>
     <row r="3" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="2"/>
       <c r="B3" s="2"/>
       <c r="C3" s="2"/>
       <c r="D3" s="2"/>
-      <c r="E3" s="3"/>
-      <c r="F3" s="4"/>
+      <c r="E3" s="2"/>
+      <c r="F3" s="3"/>
       <c r="G3" s="4"/>
       <c r="H3" s="4"/>
       <c r="I3" s="4"/>
@@ -3256,18 +3263,20 @@
       <c r="AJY3" s="4"/>
       <c r="AJZ3" s="4"/>
       <c r="AKA3" s="4"/>
+      <c r="AKB3" s="4"/>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="5" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B4" s="5"/>
       <c r="C4" s="5" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D4" s="5"/>
-      <c r="E4" s="5" t="n">
-        <f aca="false">SUM()</f>
+      <c r="E4" s="5"/>
+      <c r="F4" s="5" t="n">
+        <f aca="false">SUM(0)</f>
         <v>0</v>
       </c>
     </row>
